--- a/results/slates/slate_2026-10-15.xlsx
+++ b/results/slates/slate_2026-10-15.xlsx
@@ -1,3 +1,21 @@
+
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top SGPs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All SGPs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Legs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross-game Parlays" sheetId="4" state="visible" r:id="rId4"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
+</file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -390,4 +408,2009 @@
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>sport</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>game_key</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>p_fair</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>edge_src</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>fav</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>spread_abs</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>nfl</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Seattle Seahawks @ Denver Broncos</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Seattle Seahawks @ Denver Broncos</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Denver Broncos ML</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>+126</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Polymarket</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.4365079365079365</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.4365079365079365</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.01349206349206367</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>nfl</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Seattle Seahawks @ Denver Broncos</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Seattle Seahawks @ Denver Broncos</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Seattle Seahawks ML</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-135</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Polymarket</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5634920634920635</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.5634920634920635</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-0.01910640799529695</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>nfl</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Seattle Seahawks @ Denver Broncos</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Seattle Seahawks @ Denver Broncos</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Denver Broncos +2.5</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-102</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Polymarket</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.009803921568627416</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>nfl</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Seattle Seahawks @ Denver Broncos</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Seattle Seahawks @ Denver Broncos</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Seattle Seahawks -2.5</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-106</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Polymarket</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.02830188679245282</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>nfl</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Seattle Seahawks @ Denver Broncos</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Seattle Seahawks @ Denver Broncos</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>OVER 40.5</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-106</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Polymarket</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5108342361863488</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.5108342361863488</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.007246673071812704</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>nfl</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Seattle Seahawks @ Denver Broncos</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Seattle Seahawks @ Denver Broncos</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>UNDER 40.5</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-102</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Polymarket</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.4891657638136511</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.4891657638136511</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.03125995793767122</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ncaaf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Georgia Southern @ Old Dominion</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Georgia Southern @ Old Dominion</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Old Dominion ML</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>+148</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Polymarket</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.388333240207856</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.388333240207856</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.036933564284517</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ncaaf</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Georgia Southern @ Old Dominion</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Georgia Southern @ Old Dominion</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Georgia Southern ML</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-159</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Polymarket</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.6116667597921439</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.6116667597921439</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="b">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.003637164866885145</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ncaaf</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Georgia Southern @ Old Dominion</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Georgia Southern @ Old Dominion</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Old Dominion +3.5</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>FanDuel</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="b">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.04545454545454541</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ncaaf</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Georgia Southern @ Old Dominion</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Georgia Southern @ Old Dominion</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Georgia Southern -3.5</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>+103</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Polymarket</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.01500000000000012</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ncaaf</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Georgia Southern @ Old Dominion</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Georgia Southern @ Old Dominion</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>OVER 46.5</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>FanDuel</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.04545454545454541</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ncaaf</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Georgia Southern @ Old Dominion</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Georgia Southern @ Old Dominion</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>UNDER 46.5</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>FanDuel</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.04545454545454541</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>nba</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Toronto Raptors @ New York Knicks</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Toronto Raptors @ New York Knicks</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>New York Knicks ML</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-210</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Polymarket</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0.6499222049344299</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.6499222049344299</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.04059103081107962</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>nba</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Toronto Raptors @ New York Knicks</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Toronto Raptors @ New York Knicks</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Toronto Raptors ML</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>+191</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Polymarket</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0.3500777950655701</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.3500777950655701</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="b">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.01872638364080914</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>nba</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Toronto Raptors @ New York Knicks</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Toronto Raptors @ New York Knicks</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>New York Knicks -5.5</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-107</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Polymarket</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="b">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0.03271028037383172</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>nba</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Toronto Raptors @ New York Knicks</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Toronto Raptors @ New York Knicks</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Toronto Raptors +5.5</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-103</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Polymarket</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="b">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.0145631067961165</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>nba</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Toronto Raptors @ New York Knicks</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Toronto Raptors @ New York Knicks</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>OVER 228.5</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>228.5</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-107</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Polymarket</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0.495787700084246</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.495787700084246</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.04085930918281377</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>nba</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Toronto Raptors @ New York Knicks</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Toronto Raptors @ New York Knicks</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>UNDER 228.5</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>228.5</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-107</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Polymarket</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0.5042122999157539</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.5042122999157539</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-0.0245612515648499</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>nhl</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>St. Louis Blues @ Minnesota Wild</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>St. Louis Blues @ Minnesota Wild</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Minnesota Wild ML</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-137</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>FanDuel</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0.552982006111132</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.552982006111132</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-0.04338149307782269</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>nhl</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>St. Louis Blues @ Minnesota Wild</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>St. Louis Blues @ Minnesota Wild</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>St. Louis Blues ML</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>+130</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Polymarket</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0.4470179938888679</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.4470179938888679</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="b">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.02814138594439597</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>nhl</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>St. Louis Blues @ Minnesota Wild</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>St. Louis Blues @ Minnesota Wild</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Minnesota Wild -1.5</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>+183</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Polymarket</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0.3451251078515962</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.3451251078515962</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="b">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.02329594477998287</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>nhl</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>St. Louis Blues @ Minnesota Wild</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>St. Louis Blues @ Minnesota Wild</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>St. Louis Blues +1.5</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-201</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Polymarket</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0.6548748921484038</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.6548748921484038</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.01931670379766404</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>nhl</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>St. Louis Blues @ Minnesota Wild</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>St. Louis Blues @ Minnesota Wild</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>OVER 5.5</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-126</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Polymarket</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0.542008843967151</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.542008843967151</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.02782540685257051</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>nhl</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>St. Louis Blues @ Minnesota Wild</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>St. Louis Blues @ Minnesota Wild</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>UNDER 5.5</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>+115</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Polymarket</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0.4579911560328491</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.4579911560328491</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.01531901452937456</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>mlb</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays @ Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays @ Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians ML</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-121</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Polymarket</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0.5497259201252936</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.5497259201252936</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="b">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.004044862377602376</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>mlb</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays @ Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays @ Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays ML</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+116</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>FanDuel</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0.4502740798747064</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.4502740798747064</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="b">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.02740798747063411</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>mlb</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays @ Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays @ Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians -1.5</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+183</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Polymarket</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0.3517930095324558</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.3517930095324558</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="b">
+        <v>1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-0.004425783023150109</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>mlb</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays @ Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays @ Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays +1.5</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-201</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Polymarket</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0.6482069904675443</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.6482069904675443</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="b">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-0.02930196949885167</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>mlb</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays @ Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays @ Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>OVER 6.5</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-116</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Polymarket</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0.5149751839808318</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.5149751839808318</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-0.04108069189776165</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>mlb</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays @ Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays @ Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>UNDER 6.5</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+106</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Polymarket</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0.4850248160191682</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.4850248160191682</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-0.0008488790005134472</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>n_legs</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>legs</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>odds</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>hit_prob</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ev</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>one_in</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>stake</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>every_game</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>St. Louis Blues ML (+130) + Toronto Raptors ML (+191) + Georgia Southern -3.5 (+103) + Cleveland Guardians ML (-121) + OVER 40.5 (-106)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+4723</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.02197281936281284</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.05967065265153781</v>
+      </c>
+      <c r="G2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>No edge on most legs: backtest -82% (NFL Sundays). Shown for fun.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>